--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\chess\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EDF252-296E-48FE-83E8-44E405B56C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -29,19 +35,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>chuge</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1 基础场
@@ -51,6 +58,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>2 中级场
@@ -59,24 +67,26 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
@@ -84,13 +94,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -99,6 +110,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -221,14 +233,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,364 +246,45 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -605,326 +292,43 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1174,14 +578,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1189,19 +593,19 @@
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19.025" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
-    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
-    <col min="14" max="14" width="21.525" customWidth="1"/>
-    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="22.375" customWidth="1"/>
+    <col min="11" max="11" width="25.75" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="26.125" customWidth="1"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="15" width="23.375" customWidth="1"/>
+    <col min="16" max="16" width="26.625" customWidth="1"/>
     <col min="17" max="17" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,7 +658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -1299,7 +703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1344,7 +748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1359,7 +763,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1373,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
@@ -1405,14 +809,14 @@
       <c r="O5" s="4">
         <v>10</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1426,7 +830,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
@@ -1458,10 +862,10 @@
       <c r="O6" s="4">
         <v>10</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1475,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="1">
         <v>100003</v>
@@ -1507,10 +911,10 @@
       <c r="O7" s="4">
         <v>10</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1524,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1">
         <v>100003</v>
@@ -1556,14 +960,14 @@
       <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1577,7 +981,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="1">
         <v>100003</v>
@@ -1609,10 +1013,10 @@
       <c r="O9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1626,7 +1030,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="1">
         <v>100003</v>
@@ -1658,8 +1062,8 @@
       <c r="O10" s="4">
         <v>10</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1668,33 +1072,31 @@
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\chess\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EDF252-296E-48FE-83E8-44E405B56C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12375"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -35,20 +29,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>chuge</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1 基础场
@@ -58,7 +51,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>2 中级场
@@ -67,26 +59,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
+    <comment ref="G1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
@@ -94,14 +84,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -110,7 +99,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -233,8 +221,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,45 +240,364 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -292,43 +605,326 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -578,14 +1174,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -593,19 +1189,19 @@
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="7" max="7" width="19.025" customWidth="1"/>
     <col min="8" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="22.375" customWidth="1"/>
-    <col min="11" max="11" width="25.75" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="13" max="13" width="26.125" customWidth="1"/>
-    <col min="14" max="14" width="21.5" customWidth="1"/>
-    <col min="15" max="15" width="23.375" customWidth="1"/>
-    <col min="16" max="16" width="26.625" customWidth="1"/>
+    <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
+    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
+    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
+    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
+    <col min="14" max="14" width="21.525" customWidth="1"/>
+    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
     <col min="17" max="17" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -658,7 +1254,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -703,7 +1299,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -748,7 +1344,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:17">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -763,7 +1359,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:17">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -777,7 +1373,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
@@ -809,14 +1405,14 @@
       <c r="O5" s="4">
         <v>10</v>
       </c>
-      <c r="P5" s="5" t="s">
+      <c r="P5" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="5" t="s">
+      <c r="Q5" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:17">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -830,7 +1426,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
@@ -862,10 +1458,10 @@
       <c r="O6" s="4">
         <v>10</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="P6" s="4"/>
+      <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:17">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -879,7 +1475,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F7" s="1">
         <v>100003</v>
@@ -911,10 +1507,10 @@
       <c r="O7" s="4">
         <v>10</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="P7" s="4"/>
+      <c r="Q7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:17">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -928,7 +1524,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>100</v>
+        <v>3000</v>
       </c>
       <c r="F8" s="1">
         <v>100003</v>
@@ -960,14 +1556,14 @@
       <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="5" t="s">
+      <c r="P8" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="Q8" s="5" t="s">
+      <c r="Q8" s="4" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:17">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -981,7 +1577,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <v>1000</v>
+        <v>6000</v>
       </c>
       <c r="F9" s="1">
         <v>100003</v>
@@ -1013,10 +1609,10 @@
       <c r="O9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
+      <c r="P9" s="4"/>
+      <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:17">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1030,7 +1626,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>10000</v>
+        <v>12000</v>
       </c>
       <c r="F10" s="1">
         <v>100003</v>
@@ -1062,8 +1658,8 @@
       <c r="O10" s="4">
         <v>10</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
+      <c r="P10" s="4"/>
+      <c r="Q10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1072,31 +1668,33 @@
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\gamedoc\游戏配置表\chess\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7875E68B-E86A-4DA9-8B62-6D45D8378BDE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -29,19 +35,20 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>chuge</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0">
+    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1 基础场
@@ -51,6 +58,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>2 中级场
@@ -59,24 +67,26 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
@@ -84,13 +94,14 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -99,6 +110,7 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -221,14 +233,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="4">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-  </numFmts>
-  <fonts count="24">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -240,364 +246,45 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
+      <family val="2"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="33">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="9">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -605,326 +292,43 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1174,14 +578,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
@@ -1189,19 +593,19 @@
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19.025" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
     <col min="8" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
-    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
-    <col min="14" max="14" width="21.525" customWidth="1"/>
-    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
+    <col min="10" max="10" width="22.375" customWidth="1"/>
+    <col min="11" max="11" width="25.75" customWidth="1"/>
+    <col min="12" max="12" width="31" customWidth="1"/>
+    <col min="13" max="13" width="26.125" customWidth="1"/>
+    <col min="14" max="14" width="21.5" customWidth="1"/>
+    <col min="15" max="15" width="23.375" customWidth="1"/>
+    <col min="16" max="16" width="26.625" customWidth="1"/>
     <col min="17" max="17" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1254,7 +658,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A2" s="2" t="s">
         <v>17</v>
       </c>
@@ -1299,7 +703,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1344,7 +748,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1359,7 +763,7 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1373,7 +777,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
@@ -1405,14 +809,14 @@
       <c r="O5" s="4">
         <v>10</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Q5" s="4" t="s">
+      <c r="Q5" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1426,7 +830,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
@@ -1458,10 +862,10 @@
       <c r="O6" s="4">
         <v>10</v>
       </c>
-      <c r="P6" s="4"/>
-      <c r="Q6" s="4"/>
+      <c r="P6" s="5"/>
+      <c r="Q6" s="5"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1475,7 +879,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="1">
         <v>100003</v>
@@ -1507,10 +911,10 @@
       <c r="O7" s="4">
         <v>10</v>
       </c>
-      <c r="P7" s="4"/>
-      <c r="Q7" s="4"/>
+      <c r="P7" s="5"/>
+      <c r="Q7" s="5"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1524,7 +928,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>3000</v>
+        <v>1000</v>
       </c>
       <c r="F8" s="1">
         <v>100003</v>
@@ -1556,14 +960,14 @@
       <c r="O8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="Q8" s="4" t="s">
+      <c r="Q8" s="5" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1577,7 +981,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <v>6000</v>
+        <v>5000</v>
       </c>
       <c r="F9" s="1">
         <v>100003</v>
@@ -1609,10 +1013,10 @@
       <c r="O9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="4"/>
-      <c r="Q9" s="4"/>
+      <c r="P9" s="5"/>
+      <c r="Q9" s="5"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1626,7 +1030,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="1">
         <v>100003</v>
@@ -1658,8 +1062,8 @@
       <c r="O10" s="4">
         <v>10</v>
       </c>
-      <c r="P10" s="4"/>
-      <c r="Q10" s="4"/>
+      <c r="P10" s="5"/>
+      <c r="Q10" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1668,33 +1072,31 @@
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
   </mergeCells>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
-  <sheetPr/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData/>
+  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <headerFooter/>
 </worksheet>
 </file>
--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -63,15 +63,38 @@
       <text>
         <r>
           <rPr>
+            <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
-          <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+名次_赔付的倍数</t>
         </r>
       </text>
     </comment>
     <comment ref="H1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>赢奖 = 剩余张数 * 每张倍数 * 总投
+模式1：南方前进结算，</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -84,7 +107,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -112,7 +135,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
   <si>
     <t>id</t>
   </si>
@@ -132,6 +155,9 @@
     <t>牌池ID</t>
   </si>
   <si>
+    <t>血战结算的倍数</t>
+  </si>
+  <si>
     <t>结算剩余普通牌的倍数</t>
   </si>
   <si>
@@ -168,6 +194,9 @@
     <t>int</t>
   </si>
   <si>
+    <t>string</t>
+  </si>
+  <si>
     <t>gameId</t>
   </si>
   <si>
@@ -178,6 +207,9 @@
   </si>
   <si>
     <t>poolId</t>
+  </si>
+  <si>
+    <t>remainNormal1</t>
   </si>
   <si>
     <t>remainNormal</t>
@@ -216,6 +248,15 @@
     <t>剩余手牌结算：玩家手牌剩10张牌，一个红2，一个黑2，一个四条炸弹，押分3000
 玩家赢分=10×1×3000+4×3000+2×3000+1×8×3000
 牌局中炸弹结算：ABCD四个玩家，A出了一个红2，然后被B的三连对炸弹炸了，B被C四条炸弹炸了，C被D四连对炸弹炸了，D被A更大的四连对炸弹炸了，最终赢家为A，输家为D,并且赔付此轮所有的输分（包括A出的红2，B出的三连对，C出的四条，D出的四连对，都算在D的头上）</t>
+  </si>
+  <si>
+    <t>南方前进（血战）</t>
+  </si>
+  <si>
+    <t>3_1|4_2</t>
+  </si>
+  <si>
+    <t>最终赢分=名次赢奖+剩余手牌2赢奖+剩余炸弹赢奖（炸弹结算是在牌局中即时结算）</t>
   </si>
 </sst>
 </file>
@@ -228,13 +269,24 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="24">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -723,150 +775,171 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1180,7 +1253,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:Q10"/>
+  <dimension ref="A1:R16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1189,19 +1262,20 @@
     <col min="4" max="4" width="9" style="1"/>
     <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
     <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19.025" customWidth="1"/>
-    <col min="8" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="22.3583333333333" customWidth="1"/>
-    <col min="11" max="11" width="25.6916666666667" customWidth="1"/>
-    <col min="12" max="12" width="30.9666666666667" customWidth="1"/>
-    <col min="13" max="13" width="26.1083333333333" customWidth="1"/>
-    <col min="14" max="14" width="21.525" customWidth="1"/>
-    <col min="15" max="15" width="23.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="26.6666666666667" customWidth="1"/>
-    <col min="17" max="17" width="58.75" customWidth="1"/>
+    <col min="7" max="7" width="19" customWidth="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="22.375" customWidth="1"/>
+    <col min="12" max="12" width="25.75" customWidth="1"/>
+    <col min="13" max="13" width="31" customWidth="1"/>
+    <col min="14" max="14" width="26.125" customWidth="1"/>
+    <col min="15" max="15" width="21.5" customWidth="1"/>
+    <col min="16" max="16" width="23.375" customWidth="1"/>
+    <col min="17" max="17" width="26.625" customWidth="1"/>
+    <col min="18" max="18" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1253,98 +1327,107 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17">
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>33</v>
       </c>
     </row>
-    <row r="4" spans="1:17">
+    <row r="4" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1358,8 +1441,9 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:17">
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1367,52 +1451,53 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F5" s="1">
         <v>100003</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="3"/>
+      <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>4</v>
       </c>
-      <c r="I5" s="3">
-        <v>2</v>
-      </c>
       <c r="J5" s="3">
+        <v>2</v>
+      </c>
+      <c r="K5" s="3">
         <v>6</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>8</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>10</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>6</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>8</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>10</v>
       </c>
-      <c r="P5" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="Q5" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="6" spans="1:17">
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1420,48 +1505,49 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F6" s="1">
         <v>100003</v>
       </c>
-      <c r="G6" s="3">
+      <c r="G6" s="3"/>
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>4</v>
       </c>
-      <c r="I6" s="3">
-        <v>2</v>
-      </c>
       <c r="J6" s="3">
+        <v>2</v>
+      </c>
+      <c r="K6" s="3">
         <v>6</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>8</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>10</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>6</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>8</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>10</v>
       </c>
-      <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:17">
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1469,48 +1555,49 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F7" s="1">
         <v>100003</v>
       </c>
-      <c r="G7" s="3">
+      <c r="G7" s="3"/>
+      <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>4</v>
       </c>
-      <c r="I7" s="3">
-        <v>2</v>
-      </c>
       <c r="J7" s="3">
+        <v>2</v>
+      </c>
+      <c r="K7" s="3">
         <v>6</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>8</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>10</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>6</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="4">
         <v>8</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>10</v>
       </c>
-      <c r="P7" s="4"/>
       <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:17">
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1518,52 +1605,53 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <v>3000</v>
+        <v>100</v>
       </c>
       <c r="F8" s="1">
         <v>100003</v>
       </c>
-      <c r="G8" s="3">
+      <c r="G8" s="3"/>
+      <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4</v>
       </c>
-      <c r="I8" s="3">
-        <v>2</v>
-      </c>
       <c r="J8" s="3">
+        <v>2</v>
+      </c>
+      <c r="K8" s="3">
         <v>6</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>8</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>8</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="4" t="s">
-        <v>32</v>
-      </c>
       <c r="Q8" s="4" t="s">
-        <v>33</v>
+        <v>35</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>36</v>
       </c>
     </row>
-    <row r="9" spans="1:17">
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1571,48 +1659,49 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <v>6000</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="1">
         <v>100003</v>
       </c>
-      <c r="G9" s="3">
+      <c r="G9" s="3"/>
+      <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4</v>
       </c>
-      <c r="I9" s="3">
-        <v>2</v>
-      </c>
       <c r="J9" s="3">
+        <v>2</v>
+      </c>
+      <c r="K9" s="3">
         <v>6</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>8</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="4">
         <v>8</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:17">
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1620,53 +1709,354 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <v>12000</v>
+        <v>10000</v>
       </c>
       <c r="F10" s="1">
         <v>100003</v>
       </c>
-      <c r="G10" s="3">
+      <c r="G10" s="3"/>
+      <c r="H10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4</v>
       </c>
-      <c r="I10" s="3">
-        <v>2</v>
-      </c>
       <c r="J10" s="3">
+        <v>2</v>
+      </c>
+      <c r="K10" s="3">
         <v>6</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>8</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="4">
         <v>8</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>10</v>
       </c>
-      <c r="P10" s="4"/>
       <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
+    </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="5">
+        <v>3004011</v>
+      </c>
+      <c r="B11" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D11" s="6">
+        <v>1</v>
+      </c>
+      <c r="E11" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F11" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G11" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H11" s="8"/>
+      <c r="I11" s="7">
+        <v>2</v>
+      </c>
+      <c r="J11" s="7">
+        <v>1</v>
+      </c>
+      <c r="K11" s="7">
+        <v>2</v>
+      </c>
+      <c r="L11" s="9">
+        <v>3</v>
+      </c>
+      <c r="M11" s="9">
+        <v>4</v>
+      </c>
+      <c r="N11" s="7">
+        <v>2</v>
+      </c>
+      <c r="O11" s="9">
+        <v>3</v>
+      </c>
+      <c r="P11" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="5">
+        <v>3004012</v>
+      </c>
+      <c r="B12" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C12" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2</v>
+      </c>
+      <c r="E12" s="7">
+        <v>10000</v>
+      </c>
+      <c r="F12" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G12" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="8"/>
+      <c r="I12" s="7">
+        <v>2</v>
+      </c>
+      <c r="J12" s="7">
+        <v>1</v>
+      </c>
+      <c r="K12" s="7">
+        <v>2</v>
+      </c>
+      <c r="L12" s="9">
+        <v>3</v>
+      </c>
+      <c r="M12" s="9">
+        <v>4</v>
+      </c>
+      <c r="N12" s="7">
+        <v>2</v>
+      </c>
+      <c r="O12" s="9">
+        <v>3</v>
+      </c>
+      <c r="P12" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q12" s="11"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="5">
+        <v>3004013</v>
+      </c>
+      <c r="B13" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D13" s="5">
+        <v>3</v>
+      </c>
+      <c r="E13" s="7">
+        <v>100000</v>
+      </c>
+      <c r="F13" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G13" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H13" s="8"/>
+      <c r="I13" s="7">
+        <v>2</v>
+      </c>
+      <c r="J13" s="7">
+        <v>1</v>
+      </c>
+      <c r="K13" s="7">
+        <v>2</v>
+      </c>
+      <c r="L13" s="9">
+        <v>3</v>
+      </c>
+      <c r="M13" s="9">
+        <v>4</v>
+      </c>
+      <c r="N13" s="7">
+        <v>2</v>
+      </c>
+      <c r="O13" s="9">
+        <v>3</v>
+      </c>
+      <c r="P13" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q13" s="11"/>
+    </row>
+    <row r="14" spans="1:18">
+      <c r="A14" s="5">
+        <v>30040110</v>
+      </c>
+      <c r="B14" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C14" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="6">
+        <v>1</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1000</v>
+      </c>
+      <c r="F14" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G14" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H14" s="8"/>
+      <c r="I14" s="7">
+        <v>2</v>
+      </c>
+      <c r="J14" s="7">
+        <v>1</v>
+      </c>
+      <c r="K14" s="7">
+        <v>2</v>
+      </c>
+      <c r="L14" s="9">
+        <v>3</v>
+      </c>
+      <c r="M14" s="9">
+        <v>4</v>
+      </c>
+      <c r="N14" s="7">
+        <v>2</v>
+      </c>
+      <c r="O14" s="9">
+        <v>3</v>
+      </c>
+      <c r="P14" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18">
+      <c r="A15" s="5">
+        <v>30040111</v>
+      </c>
+      <c r="B15" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C15" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2</v>
+      </c>
+      <c r="E15" s="7">
+        <v>10000</v>
+      </c>
+      <c r="F15" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G15" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H15" s="8"/>
+      <c r="I15" s="7">
+        <v>2</v>
+      </c>
+      <c r="J15" s="7">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7">
+        <v>2</v>
+      </c>
+      <c r="L15" s="9">
+        <v>3</v>
+      </c>
+      <c r="M15" s="9">
+        <v>4</v>
+      </c>
+      <c r="N15" s="7">
+        <v>2</v>
+      </c>
+      <c r="O15" s="9">
+        <v>3</v>
+      </c>
+      <c r="P15" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q15" s="11"/>
+    </row>
+    <row r="16" spans="1:18">
+      <c r="A16" s="5">
+        <v>30040112</v>
+      </c>
+      <c r="B16" s="6">
+        <v>300401</v>
+      </c>
+      <c r="C16" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="D16" s="5">
+        <v>3</v>
+      </c>
+      <c r="E16" s="7">
+        <v>100000</v>
+      </c>
+      <c r="F16" s="5">
+        <v>100003</v>
+      </c>
+      <c r="G16" s="8" t="s">
+        <v>38</v>
+      </c>
+      <c r="H16" s="8"/>
+      <c r="I16" s="7">
+        <v>2</v>
+      </c>
+      <c r="J16" s="7">
+        <v>1</v>
+      </c>
+      <c r="K16" s="7">
+        <v>2</v>
+      </c>
+      <c r="L16" s="9">
+        <v>3</v>
+      </c>
+      <c r="M16" s="9">
+        <v>4</v>
+      </c>
+      <c r="N16" s="7">
+        <v>2</v>
+      </c>
+      <c r="O16" s="9">
+        <v>3</v>
+      </c>
+      <c r="P16" s="9">
+        <v>4</v>
+      </c>
+      <c r="Q16" s="11"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="P8:P10"/>
+  <mergeCells count="6">
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="Q11:Q13"/>
+    <mergeCell ref="Q14:Q16"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="R8:R10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\cehua\gamedoc\游戏配置表\chess\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04EDF252-296E-48FE-83E8-44E405B56C0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="28800" windowHeight="12255"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -35,20 +29,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <authors>
     <author>chuge</author>
     <author>Administrator</author>
   </authors>
   <commentList>
-    <comment ref="D1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
+    <comment ref="D1" authorId="0">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">1 基础场
@@ -58,7 +51,6 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>2 中级场
@@ -67,41 +59,13 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000002000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="H1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000003000000}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
-</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="I1" authorId="1" shapeId="0" xr:uid="{00000000-0006-0000-0000-000004000000}">
+    <comment ref="E1" authorId="1">
       <text>
         <r>
           <rPr>
             <b/>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>Administrator:</t>
@@ -110,7 +74,53 @@
           <rPr>
             <sz val="9"/>
             <rFont val="宋体"/>
-            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+低于这个金额时，用户会被踢出房间</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>赢奖 = 剩余张数 * 每张倍数 * 总投</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="I1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">赢奖 = 剩余红2的张数 * 每张倍数 * 总投
+</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="J1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -124,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
   <si>
     <t>id</t>
   </si>
@@ -138,6 +148,9 @@
     <t>房间类型</t>
   </si>
   <si>
+    <t>游戏最低准备金额</t>
+  </si>
+  <si>
     <t>押分列表</t>
   </si>
   <si>
@@ -184,6 +197,9 @@
   </si>
   <si>
     <t>roomId</t>
+  </si>
+  <si>
+    <t>prepareamount</t>
   </si>
   <si>
     <t>betList</t>
@@ -233,8 +249,14 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -246,45 +268,364 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="微软雅黑"/>
-      <family val="2"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="9"/>
       <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -292,13 +633,255 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -314,21 +897,62 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -578,34 +1202,34 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:R10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="9" width="18.875" customWidth="1"/>
-    <col min="10" max="10" width="22.375" customWidth="1"/>
-    <col min="11" max="11" width="25.75" customWidth="1"/>
-    <col min="12" max="12" width="31" customWidth="1"/>
-    <col min="13" max="13" width="26.125" customWidth="1"/>
-    <col min="14" max="14" width="21.5" customWidth="1"/>
-    <col min="15" max="15" width="23.375" customWidth="1"/>
-    <col min="16" max="16" width="26.625" customWidth="1"/>
-    <col min="17" max="17" width="58.75" customWidth="1"/>
+    <col min="5" max="6" width="21.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="8" width="19" customWidth="1"/>
+    <col min="9" max="10" width="18.875" customWidth="1"/>
+    <col min="11" max="11" width="22.375" customWidth="1"/>
+    <col min="12" max="12" width="25.75" customWidth="1"/>
+    <col min="13" max="13" width="31" customWidth="1"/>
+    <col min="14" max="14" width="26.125" customWidth="1"/>
+    <col min="15" max="15" width="21.5" customWidth="1"/>
+    <col min="16" max="16" width="23.375" customWidth="1"/>
+    <col min="17" max="17" width="26.625" customWidth="1"/>
+    <col min="18" max="18" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:18">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -657,98 +1281,107 @@
       <c r="Q1" s="2" t="s">
         <v>16</v>
       </c>
+      <c r="R1" s="2" t="s">
+        <v>17</v>
+      </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:18">
       <c r="A2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>18</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:18">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>32</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="4" spans="1:18">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -762,8 +1395,9 @@
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
+      <c r="N4" s="2"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="5" spans="1:18">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -771,52 +1405,56 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="3">
+        <f>F5*52</f>
+        <v>5200</v>
+      </c>
+      <c r="F5" s="3">
         <v>100</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>100003</v>
       </c>
-      <c r="G5" s="3">
+      <c r="H5" s="3">
         <v>1</v>
       </c>
-      <c r="H5" s="3">
+      <c r="I5" s="3">
         <v>4</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>2</v>
       </c>
-      <c r="J5" s="3">
+      <c r="K5" s="3">
         <v>6</v>
       </c>
-      <c r="K5" s="4">
+      <c r="L5" s="4">
         <v>8</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>10</v>
       </c>
-      <c r="M5" s="3">
+      <c r="N5" s="3">
         <v>6</v>
       </c>
-      <c r="N5" s="4">
+      <c r="O5" s="4">
         <v>8</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>10</v>
       </c>
-      <c r="P5" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q5" s="5" t="s">
-        <v>33</v>
+      <c r="Q5" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="6" spans="1:18">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -824,48 +1462,52 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="3">
+        <f>F6*52</f>
+        <v>52000</v>
+      </c>
+      <c r="F6" s="3">
         <v>1000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>100003</v>
       </c>
-      <c r="G6" s="3">
+      <c r="H6" s="3">
         <v>1</v>
       </c>
-      <c r="H6" s="3">
+      <c r="I6" s="3">
         <v>4</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>2</v>
       </c>
-      <c r="J6" s="3">
+      <c r="K6" s="3">
         <v>6</v>
       </c>
-      <c r="K6" s="4">
+      <c r="L6" s="4">
         <v>8</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>10</v>
       </c>
-      <c r="M6" s="3">
+      <c r="N6" s="3">
         <v>6</v>
       </c>
-      <c r="N6" s="4">
+      <c r="O6" s="4">
         <v>8</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>10</v>
       </c>
-      <c r="P6" s="5"/>
-      <c r="Q6" s="5"/>
+      <c r="Q6" s="4"/>
+      <c r="R6" s="4"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="7" spans="1:18">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -873,48 +1515,52 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="3">
+        <f>F7*52</f>
+        <v>520000</v>
+      </c>
+      <c r="F7" s="3">
         <v>10000</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>100003</v>
       </c>
-      <c r="G7" s="3">
+      <c r="H7" s="3">
         <v>1</v>
       </c>
-      <c r="H7" s="3">
+      <c r="I7" s="3">
         <v>4</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>2</v>
       </c>
-      <c r="J7" s="3">
+      <c r="K7" s="3">
         <v>6</v>
       </c>
-      <c r="K7" s="4">
+      <c r="L7" s="4">
         <v>8</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>10</v>
       </c>
-      <c r="M7" s="3">
+      <c r="N7" s="3">
         <v>6</v>
       </c>
-      <c r="N7" s="4">
+      <c r="O7" s="4">
         <v>8</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>10</v>
       </c>
-      <c r="P7" s="5"/>
-      <c r="Q7" s="5"/>
+      <c r="Q7" s="4"/>
+      <c r="R7" s="4"/>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="8" spans="1:18">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -922,52 +1568,56 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="3">
+        <f>F8*52</f>
+        <v>5200</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>100003</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>4</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>6</v>
       </c>
-      <c r="K8" s="4">
+      <c r="L8" s="4">
         <v>8</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>10</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>6</v>
       </c>
-      <c r="N8" s="4">
+      <c r="O8" s="4">
         <v>8</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>10</v>
       </c>
-      <c r="P8" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="Q8" s="5" t="s">
-        <v>33</v>
+      <c r="Q8" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R8" s="4" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="9" spans="1:18">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -975,48 +1625,52 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="3">
+        <f>F9*52</f>
+        <v>52000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>100003</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>4</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>6</v>
       </c>
-      <c r="K9" s="4">
+      <c r="L9" s="4">
         <v>8</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>10</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>6</v>
       </c>
-      <c r="N9" s="4">
+      <c r="O9" s="4">
         <v>8</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>10</v>
       </c>
-      <c r="P9" s="5"/>
-      <c r="Q9" s="5"/>
+      <c r="Q9" s="4"/>
+      <c r="R9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.15">
+    <row r="10" spans="1:18">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1024,79 +1678,85 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="3">
+        <f>F10*52</f>
+        <v>520000</v>
+      </c>
+      <c r="F10" s="3">
         <v>10000</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>100003</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>1</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>4</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>2</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>6</v>
       </c>
-      <c r="K10" s="4">
+      <c r="L10" s="4">
         <v>8</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>10</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>6</v>
       </c>
-      <c r="N10" s="4">
+      <c r="O10" s="4">
         <v>8</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>10</v>
       </c>
-      <c r="P10" s="5"/>
-      <c r="Q10" s="5"/>
+      <c r="Q10" s="4"/>
+      <c r="R10" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="4">
-    <mergeCell ref="P5:P7"/>
-    <mergeCell ref="P8:P10"/>
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="R5:R7"/>
+    <mergeCell ref="R8:R10"/>
   </mergeCells>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <headerFooter/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.5"/>
   <sheetData/>
-  <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -59,7 +59,29 @@
         </r>
       </text>
     </comment>
-    <comment ref="G1" authorId="1">
+    <comment ref="E1" authorId="1">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>Administrator:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+低于这个金额时，用户会被踢出房间</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="H1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -81,7 +103,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="H1" authorId="1">
+    <comment ref="I1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -94,7 +116,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="I1" authorId="1">
+    <comment ref="J1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -107,7 +129,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="J1" authorId="1">
+    <comment ref="K1" authorId="1">
       <text>
         <r>
           <rPr>
@@ -135,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="40">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
   <si>
     <t>id</t>
   </si>
@@ -149,6 +171,9 @@
     <t>房间类型</t>
   </si>
   <si>
+    <t>游戏最低准备金额</t>
+  </si>
+  <si>
     <t>押分列表</t>
   </si>
   <si>
@@ -201,6 +226,9 @@
   </si>
   <si>
     <t>roomId</t>
+  </si>
+  <si>
+    <t>prepareamount</t>
   </si>
   <si>
     <t>betList</t>
@@ -269,24 +297,13 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="微软雅黑"/>
-      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
@@ -775,137 +792,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -919,27 +936,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1253,29 +1249,28 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
     <col min="2" max="2" width="12" style="1" customWidth="1"/>
     <col min="3" max="3" width="15.75" style="1" customWidth="1"/>
     <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="21.25" style="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="1"/>
-    <col min="7" max="7" width="19" customWidth="1"/>
-    <col min="8" max="8" width="19" customWidth="1"/>
-    <col min="9" max="10" width="18.875" customWidth="1"/>
-    <col min="11" max="11" width="22.375" customWidth="1"/>
-    <col min="12" max="12" width="25.75" customWidth="1"/>
-    <col min="13" max="13" width="31" customWidth="1"/>
-    <col min="14" max="14" width="26.125" customWidth="1"/>
-    <col min="15" max="15" width="21.5" customWidth="1"/>
-    <col min="16" max="16" width="23.375" customWidth="1"/>
-    <col min="17" max="17" width="26.625" customWidth="1"/>
-    <col min="18" max="18" width="58.75" customWidth="1"/>
+    <col min="5" max="6" width="21.25" style="1" customWidth="1"/>
+    <col min="7" max="7" width="9" style="1"/>
+    <col min="8" max="9" width="19" customWidth="1"/>
+    <col min="10" max="11" width="18.875" customWidth="1"/>
+    <col min="12" max="12" width="22.375" customWidth="1"/>
+    <col min="13" max="13" width="25.75" customWidth="1"/>
+    <col min="14" max="14" width="31" customWidth="1"/>
+    <col min="15" max="15" width="26.125" customWidth="1"/>
+    <col min="16" max="16" width="21.5" customWidth="1"/>
+    <col min="17" max="17" width="23.375" customWidth="1"/>
+    <col min="18" max="18" width="26.625" customWidth="1"/>
+    <col min="19" max="19" width="58.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1330,104 +1325,113 @@
       <c r="R1" s="2" t="s">
         <v>17</v>
       </c>
+      <c r="S1" s="2" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="2" spans="1:18">
+    <row r="2" spans="1:19">
       <c r="A2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G2" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>19</v>
       </c>
     </row>
-    <row r="3" spans="1:18">
+    <row r="3" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>35</v>
       </c>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2"/>
       <c r="B4" s="2"/>
       <c r="C4" s="2"/>
@@ -1442,8 +1446,9 @@
       <c r="L4" s="2"/>
       <c r="M4" s="2"/>
       <c r="N4" s="2"/>
+      <c r="O4" s="2"/>
     </row>
-    <row r="5" spans="1:18">
+    <row r="5" spans="1:19">
       <c r="A5" s="1">
         <v>3004001</v>
       </c>
@@ -1451,53 +1456,57 @@
         <v>300400</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D5" s="2">
         <v>1</v>
       </c>
       <c r="E5" s="3">
+        <f>F5*52</f>
+        <v>5200</v>
+      </c>
+      <c r="F5" s="3">
         <v>100</v>
       </c>
-      <c r="F5" s="1">
+      <c r="G5" s="1">
         <v>100003</v>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3">
+      <c r="H5" s="3"/>
+      <c r="I5" s="3">
         <v>1</v>
       </c>
-      <c r="I5" s="3">
+      <c r="J5" s="3">
         <v>4</v>
       </c>
-      <c r="J5" s="3">
-        <v>2</v>
-      </c>
       <c r="K5" s="3">
+        <v>2</v>
+      </c>
+      <c r="L5" s="3">
         <v>6</v>
       </c>
-      <c r="L5" s="4">
+      <c r="M5" s="4">
         <v>8</v>
       </c>
-      <c r="M5" s="4">
+      <c r="N5" s="4">
         <v>10</v>
       </c>
-      <c r="N5" s="3">
+      <c r="O5" s="3">
         <v>6</v>
       </c>
-      <c r="O5" s="4">
+      <c r="P5" s="4">
         <v>8</v>
       </c>
-      <c r="P5" s="4">
+      <c r="Q5" s="4">
         <v>10</v>
       </c>
-      <c r="Q5" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="R5" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="6" spans="1:18">
+    <row r="6" spans="1:19">
       <c r="A6" s="1">
         <v>3004002</v>
       </c>
@@ -1505,49 +1514,53 @@
         <v>300400</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D6" s="1">
         <v>2</v>
       </c>
       <c r="E6" s="3">
+        <f>F6*52</f>
+        <v>52000</v>
+      </c>
+      <c r="F6" s="3">
         <v>1000</v>
       </c>
-      <c r="F6" s="1">
+      <c r="G6" s="1">
         <v>100003</v>
       </c>
-      <c r="G6" s="3"/>
-      <c r="H6" s="3">
+      <c r="H6" s="3"/>
+      <c r="I6" s="3">
         <v>1</v>
       </c>
-      <c r="I6" s="3">
+      <c r="J6" s="3">
         <v>4</v>
       </c>
-      <c r="J6" s="3">
-        <v>2</v>
-      </c>
       <c r="K6" s="3">
+        <v>2</v>
+      </c>
+      <c r="L6" s="3">
         <v>6</v>
       </c>
-      <c r="L6" s="4">
+      <c r="M6" s="4">
         <v>8</v>
       </c>
-      <c r="M6" s="4">
+      <c r="N6" s="4">
         <v>10</v>
       </c>
-      <c r="N6" s="3">
+      <c r="O6" s="3">
         <v>6</v>
       </c>
-      <c r="O6" s="4">
+      <c r="P6" s="4">
         <v>8</v>
       </c>
-      <c r="P6" s="4">
+      <c r="Q6" s="4">
         <v>10</v>
       </c>
-      <c r="Q6" s="4"/>
       <c r="R6" s="4"/>
+      <c r="S6" s="4"/>
     </row>
-    <row r="7" spans="1:18">
+    <row r="7" spans="1:19">
       <c r="A7" s="1">
         <v>3004003</v>
       </c>
@@ -1555,49 +1568,53 @@
         <v>300400</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D7" s="1">
         <v>3</v>
       </c>
       <c r="E7" s="3">
+        <f>F7*52</f>
+        <v>520000</v>
+      </c>
+      <c r="F7" s="3">
         <v>10000</v>
       </c>
-      <c r="F7" s="1">
+      <c r="G7" s="1">
         <v>100003</v>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3">
+      <c r="H7" s="3"/>
+      <c r="I7" s="3">
         <v>1</v>
       </c>
-      <c r="I7" s="3">
+      <c r="J7" s="3">
         <v>4</v>
       </c>
-      <c r="J7" s="3">
-        <v>2</v>
-      </c>
       <c r="K7" s="3">
+        <v>2</v>
+      </c>
+      <c r="L7" s="3">
         <v>6</v>
       </c>
-      <c r="L7" s="4">
+      <c r="M7" s="4">
         <v>8</v>
       </c>
-      <c r="M7" s="4">
+      <c r="N7" s="4">
         <v>10</v>
       </c>
-      <c r="N7" s="3">
+      <c r="O7" s="3">
         <v>6</v>
       </c>
-      <c r="O7" s="4">
+      <c r="P7" s="4">
         <v>8</v>
       </c>
-      <c r="P7" s="4">
+      <c r="Q7" s="4">
         <v>10</v>
       </c>
-      <c r="Q7" s="4"/>
       <c r="R7" s="4"/>
+      <c r="S7" s="4"/>
     </row>
-    <row r="8" spans="1:18">
+    <row r="8" spans="1:19">
       <c r="A8" s="1">
         <v>30040010</v>
       </c>
@@ -1605,53 +1622,57 @@
         <v>300400</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D8" s="2">
         <v>1</v>
       </c>
       <c r="E8" s="3">
+        <f>F8*52</f>
+        <v>5200</v>
+      </c>
+      <c r="F8" s="3">
         <v>100</v>
       </c>
-      <c r="F8" s="1">
+      <c r="G8" s="1">
         <v>100003</v>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="3">
+      <c r="H8" s="3"/>
+      <c r="I8" s="3">
         <v>1</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>4</v>
       </c>
-      <c r="J8" s="3">
-        <v>2</v>
-      </c>
       <c r="K8" s="3">
+        <v>2</v>
+      </c>
+      <c r="L8" s="3">
         <v>6</v>
       </c>
-      <c r="L8" s="4">
+      <c r="M8" s="4">
         <v>8</v>
       </c>
-      <c r="M8" s="4">
+      <c r="N8" s="4">
         <v>10</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>6</v>
       </c>
-      <c r="O8" s="4">
+      <c r="P8" s="4">
         <v>8</v>
       </c>
-      <c r="P8" s="4">
+      <c r="Q8" s="4">
         <v>10</v>
       </c>
-      <c r="Q8" s="4" t="s">
-        <v>35</v>
-      </c>
       <c r="R8" s="4" t="s">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="S8" s="4" t="s">
+        <v>38</v>
       </c>
     </row>
-    <row r="9" spans="1:18">
+    <row r="9" spans="1:19">
       <c r="A9" s="1">
         <v>30040011</v>
       </c>
@@ -1659,49 +1680,53 @@
         <v>300400</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9" s="1">
         <v>2</v>
       </c>
       <c r="E9" s="3">
+        <f>F9*52</f>
+        <v>52000</v>
+      </c>
+      <c r="F9" s="3">
         <v>1000</v>
       </c>
-      <c r="F9" s="1">
+      <c r="G9" s="1">
         <v>100003</v>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3">
+      <c r="H9" s="3"/>
+      <c r="I9" s="3">
         <v>1</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>4</v>
       </c>
-      <c r="J9" s="3">
-        <v>2</v>
-      </c>
       <c r="K9" s="3">
+        <v>2</v>
+      </c>
+      <c r="L9" s="3">
         <v>6</v>
       </c>
-      <c r="L9" s="4">
+      <c r="M9" s="4">
         <v>8</v>
       </c>
-      <c r="M9" s="4">
+      <c r="N9" s="4">
         <v>10</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>6</v>
       </c>
-      <c r="O9" s="4">
+      <c r="P9" s="4">
         <v>8</v>
       </c>
-      <c r="P9" s="4">
+      <c r="Q9" s="4">
         <v>10</v>
       </c>
-      <c r="Q9" s="4"/>
       <c r="R9" s="4"/>
+      <c r="S9" s="4"/>
     </row>
-    <row r="10" spans="1:18">
+    <row r="10" spans="1:19">
       <c r="A10" s="1">
         <v>30040012</v>
       </c>
@@ -1709,354 +1734,382 @@
         <v>300400</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D10" s="1">
         <v>3</v>
       </c>
       <c r="E10" s="3">
+        <f>F10*52</f>
+        <v>520000</v>
+      </c>
+      <c r="F10" s="3">
         <v>10000</v>
       </c>
-      <c r="F10" s="1">
+      <c r="G10" s="1">
         <v>100003</v>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="3">
+      <c r="H10" s="3"/>
+      <c r="I10" s="3">
         <v>1</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>4</v>
       </c>
-      <c r="J10" s="3">
-        <v>2</v>
-      </c>
       <c r="K10" s="3">
+        <v>2</v>
+      </c>
+      <c r="L10" s="3">
         <v>6</v>
       </c>
-      <c r="L10" s="4">
+      <c r="M10" s="4">
         <v>8</v>
       </c>
-      <c r="M10" s="4">
+      <c r="N10" s="4">
         <v>10</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>6</v>
       </c>
-      <c r="O10" s="4">
+      <c r="P10" s="4">
         <v>8</v>
       </c>
-      <c r="P10" s="4">
+      <c r="Q10" s="4">
         <v>10</v>
       </c>
-      <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
+      <c r="S10" s="4"/>
     </row>
-    <row r="11" spans="1:18">
-      <c r="A11" s="5">
+    <row r="11" spans="1:19">
+      <c r="A11" s="1">
         <v>3004011</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11" s="2">
         <v>300401</v>
       </c>
-      <c r="C11" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="6">
+      <c r="C11" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="2">
         <v>1</v>
       </c>
-      <c r="E11" s="7">
+      <c r="E11" s="3">
+        <f>F11*12</f>
+        <v>12000</v>
+      </c>
+      <c r="F11" s="3">
         <v>1000</v>
       </c>
-      <c r="F11" s="5">
+      <c r="G11" s="1">
         <v>100003</v>
       </c>
-      <c r="G11" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="8"/>
-      <c r="I11" s="7">
-        <v>2</v>
-      </c>
-      <c r="J11" s="7">
+      <c r="H11" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I11" s="3"/>
+      <c r="J11" s="3">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
         <v>1</v>
       </c>
-      <c r="K11" s="7">
-        <v>2</v>
-      </c>
-      <c r="L11" s="9">
+      <c r="L11" s="3">
+        <v>2</v>
+      </c>
+      <c r="M11" s="4">
         <v>3</v>
       </c>
-      <c r="M11" s="9">
+      <c r="N11" s="4">
         <v>4</v>
       </c>
-      <c r="N11" s="7">
-        <v>2</v>
-      </c>
-      <c r="O11" s="9">
+      <c r="O11" s="3">
+        <v>2</v>
+      </c>
+      <c r="P11" s="4">
         <v>3</v>
       </c>
-      <c r="P11" s="9">
+      <c r="Q11" s="4">
         <v>4</v>
       </c>
-      <c r="Q11" s="10" t="s">
+      <c r="R11" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
+      <c r="A12" s="1">
+        <v>3004012</v>
+      </c>
+      <c r="B12" s="2">
+        <v>300401</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>39</v>
       </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <f>F12*12</f>
+        <v>120000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H12" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I12" s="3"/>
+      <c r="J12" s="3">
+        <v>2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>1</v>
+      </c>
+      <c r="L12" s="3">
+        <v>2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>3</v>
+      </c>
+      <c r="N12" s="4">
+        <v>4</v>
+      </c>
+      <c r="O12" s="3">
+        <v>2</v>
+      </c>
+      <c r="P12" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q12" s="4">
+        <v>4</v>
+      </c>
+      <c r="R12" s="4"/>
     </row>
-    <row r="12" spans="1:18">
-      <c r="A12" s="5">
-        <v>3004012</v>
-      </c>
-      <c r="B12" s="6">
+    <row r="13" spans="1:19">
+      <c r="A13" s="1">
+        <v>3004013</v>
+      </c>
+      <c r="B13" s="2">
         <v>300401</v>
       </c>
-      <c r="C12" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D12" s="5">
-        <v>2</v>
-      </c>
-      <c r="E12" s="7">
+      <c r="C13" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3">
+        <f>F13*12</f>
+        <v>1200000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>100000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H13" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I13" s="3"/>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>1</v>
+      </c>
+      <c r="L13" s="3">
+        <v>2</v>
+      </c>
+      <c r="M13" s="4">
+        <v>3</v>
+      </c>
+      <c r="N13" s="4">
+        <v>4</v>
+      </c>
+      <c r="O13" s="3">
+        <v>2</v>
+      </c>
+      <c r="P13" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q13" s="4">
+        <v>4</v>
+      </c>
+      <c r="R13" s="4"/>
+    </row>
+    <row r="14" spans="1:19">
+      <c r="A14" s="1">
+        <v>30040110</v>
+      </c>
+      <c r="B14" s="2">
+        <v>300401</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D14" s="2">
+        <v>1</v>
+      </c>
+      <c r="E14" s="3">
+        <f>F14*12</f>
+        <v>12000</v>
+      </c>
+      <c r="F14" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G14" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I14" s="3"/>
+      <c r="J14" s="3">
+        <v>2</v>
+      </c>
+      <c r="K14" s="3">
+        <v>1</v>
+      </c>
+      <c r="L14" s="3">
+        <v>2</v>
+      </c>
+      <c r="M14" s="4">
+        <v>3</v>
+      </c>
+      <c r="N14" s="4">
+        <v>4</v>
+      </c>
+      <c r="O14" s="3">
+        <v>2</v>
+      </c>
+      <c r="P14" s="4">
+        <v>3</v>
+      </c>
+      <c r="Q14" s="4">
+        <v>4</v>
+      </c>
+      <c r="R14" s="4" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
+      <c r="A15" s="1">
+        <v>30040111</v>
+      </c>
+      <c r="B15" s="2">
+        <v>300401</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D15" s="1">
+        <v>2</v>
+      </c>
+      <c r="E15" s="3">
+        <f>F15*12</f>
+        <v>120000</v>
+      </c>
+      <c r="F15" s="3">
         <v>10000</v>
       </c>
-      <c r="F12" s="5">
+      <c r="G15" s="1">
         <v>100003</v>
       </c>
-      <c r="G12" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="8"/>
-      <c r="I12" s="7">
-        <v>2</v>
-      </c>
-      <c r="J12" s="7">
+      <c r="H15" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I15" s="3"/>
+      <c r="J15" s="3">
+        <v>2</v>
+      </c>
+      <c r="K15" s="3">
         <v>1</v>
       </c>
-      <c r="K12" s="7">
-        <v>2</v>
-      </c>
-      <c r="L12" s="9">
+      <c r="L15" s="3">
+        <v>2</v>
+      </c>
+      <c r="M15" s="4">
         <v>3</v>
       </c>
-      <c r="M12" s="9">
+      <c r="N15" s="4">
         <v>4</v>
       </c>
-      <c r="N12" s="7">
-        <v>2</v>
-      </c>
-      <c r="O12" s="9">
+      <c r="O15" s="3">
+        <v>2</v>
+      </c>
+      <c r="P15" s="4">
         <v>3</v>
       </c>
-      <c r="P12" s="9">
+      <c r="Q15" s="4">
         <v>4</v>
       </c>
-      <c r="Q12" s="11"/>
+      <c r="R15" s="4"/>
     </row>
-    <row r="13" spans="1:18">
-      <c r="A13" s="5">
-        <v>3004013</v>
-      </c>
-      <c r="B13" s="6">
+    <row r="16" spans="1:19">
+      <c r="A16" s="1">
+        <v>30040112</v>
+      </c>
+      <c r="B16" s="2">
         <v>300401</v>
       </c>
-      <c r="C13" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C16" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="D16" s="1">
         <v>3</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E16" s="3">
+        <f>F16*12</f>
+        <v>1200000</v>
+      </c>
+      <c r="F16" s="3">
         <v>100000</v>
       </c>
-      <c r="F13" s="5">
+      <c r="G16" s="1">
         <v>100003</v>
       </c>
-      <c r="G13" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H13" s="8"/>
-      <c r="I13" s="7">
-        <v>2</v>
-      </c>
-      <c r="J13" s="7">
+      <c r="H16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="I16" s="3"/>
+      <c r="J16" s="3">
+        <v>2</v>
+      </c>
+      <c r="K16" s="3">
         <v>1</v>
       </c>
-      <c r="K13" s="7">
-        <v>2</v>
-      </c>
-      <c r="L13" s="9">
+      <c r="L16" s="3">
+        <v>2</v>
+      </c>
+      <c r="M16" s="4">
         <v>3</v>
       </c>
-      <c r="M13" s="9">
+      <c r="N16" s="4">
         <v>4</v>
       </c>
-      <c r="N13" s="7">
-        <v>2</v>
-      </c>
-      <c r="O13" s="9">
+      <c r="O16" s="3">
+        <v>2</v>
+      </c>
+      <c r="P16" s="4">
         <v>3</v>
       </c>
-      <c r="P13" s="9">
+      <c r="Q16" s="4">
         <v>4</v>
       </c>
-      <c r="Q13" s="11"/>
-    </row>
-    <row r="14" spans="1:18">
-      <c r="A14" s="5">
-        <v>30040110</v>
-      </c>
-      <c r="B14" s="6">
-        <v>300401</v>
-      </c>
-      <c r="C14" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D14" s="6">
-        <v>1</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1000</v>
-      </c>
-      <c r="F14" s="5">
-        <v>100003</v>
-      </c>
-      <c r="G14" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H14" s="8"/>
-      <c r="I14" s="7">
-        <v>2</v>
-      </c>
-      <c r="J14" s="7">
-        <v>1</v>
-      </c>
-      <c r="K14" s="7">
-        <v>2</v>
-      </c>
-      <c r="L14" s="9">
-        <v>3</v>
-      </c>
-      <c r="M14" s="9">
-        <v>4</v>
-      </c>
-      <c r="N14" s="7">
-        <v>2</v>
-      </c>
-      <c r="O14" s="9">
-        <v>3</v>
-      </c>
-      <c r="P14" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q14" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
-      <c r="A15" s="5">
-        <v>30040111</v>
-      </c>
-      <c r="B15" s="6">
-        <v>300401</v>
-      </c>
-      <c r="C15" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D15" s="5">
-        <v>2</v>
-      </c>
-      <c r="E15" s="7">
-        <v>10000</v>
-      </c>
-      <c r="F15" s="5">
-        <v>100003</v>
-      </c>
-      <c r="G15" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H15" s="8"/>
-      <c r="I15" s="7">
-        <v>2</v>
-      </c>
-      <c r="J15" s="7">
-        <v>1</v>
-      </c>
-      <c r="K15" s="7">
-        <v>2</v>
-      </c>
-      <c r="L15" s="9">
-        <v>3</v>
-      </c>
-      <c r="M15" s="9">
-        <v>4</v>
-      </c>
-      <c r="N15" s="7">
-        <v>2</v>
-      </c>
-      <c r="O15" s="9">
-        <v>3</v>
-      </c>
-      <c r="P15" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q15" s="11"/>
-    </row>
-    <row r="16" spans="1:18">
-      <c r="A16" s="5">
-        <v>30040112</v>
-      </c>
-      <c r="B16" s="6">
-        <v>300401</v>
-      </c>
-      <c r="C16" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="D16" s="5">
-        <v>3</v>
-      </c>
-      <c r="E16" s="7">
-        <v>100000</v>
-      </c>
-      <c r="F16" s="5">
-        <v>100003</v>
-      </c>
-      <c r="G16" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="H16" s="8"/>
-      <c r="I16" s="7">
-        <v>2</v>
-      </c>
-      <c r="J16" s="7">
-        <v>1</v>
-      </c>
-      <c r="K16" s="7">
-        <v>2</v>
-      </c>
-      <c r="L16" s="9">
-        <v>3</v>
-      </c>
-      <c r="M16" s="9">
-        <v>4</v>
-      </c>
-      <c r="N16" s="7">
-        <v>2</v>
-      </c>
-      <c r="O16" s="9">
-        <v>3</v>
-      </c>
-      <c r="P16" s="9">
-        <v>4</v>
-      </c>
-      <c r="Q16" s="11"/>
+      <c r="R16" s="4"/>
     </row>
   </sheetData>
   <mergeCells count="6">
-    <mergeCell ref="Q5:Q7"/>
-    <mergeCell ref="Q8:Q10"/>
-    <mergeCell ref="Q11:Q13"/>
-    <mergeCell ref="Q14:Q16"/>
     <mergeCell ref="R5:R7"/>
     <mergeCell ref="R8:R10"/>
+    <mergeCell ref="R11:R13"/>
+    <mergeCell ref="R14:R16"/>
+    <mergeCell ref="S5:S7"/>
+    <mergeCell ref="S8:S10"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -134,7 +134,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="63" uniqueCount="37">
   <si>
     <t>id</t>
   </si>
@@ -244,6 +244,9 @@
     <t>剩余手牌结算：玩家手牌剩10张牌，一个红2，一个黑2，一个四条炸弹，押分3000
 玩家赢分=10×1×3000+4×3000+2×3000+1×8×3000
 牌局中炸弹结算：ABCD四个玩家，A出了一个红2，然后被B的三连对炸弹炸了，B被C四条炸弹炸了，C被D四连对炸弹炸了，D被A更大的四连对炸弹炸了，最终赢家为A，输家为D,并且赔付此轮所有的输分（包括A出的红2，B出的三连对，C出的四条，D出的四连对，都算在D的头上）</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
   </si>
 </sst>
 </file>
@@ -1208,7 +1211,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R10"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1411,7 +1414,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <f>F5*52</f>
+        <f t="shared" ref="E5:E13" si="0">F5*52</f>
         <v>5200</v>
       </c>
       <c r="F5" s="3">
@@ -1468,7 +1471,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>F6*52</f>
+        <f t="shared" si="0"/>
         <v>52000</v>
       </c>
       <c r="F6" s="3">
@@ -1521,7 +1524,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <f>F7*52</f>
+        <f t="shared" si="0"/>
         <v>520000</v>
       </c>
       <c r="F7" s="3">
@@ -1574,7 +1577,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <f>F8*52</f>
+        <f t="shared" si="0"/>
         <v>5200</v>
       </c>
       <c r="F8" s="3">
@@ -1631,7 +1634,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f>F9*52</f>
+        <f t="shared" si="0"/>
         <v>52000</v>
       </c>
       <c r="F9" s="3">
@@ -1684,7 +1687,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <f>F10*52</f>
+        <f t="shared" si="0"/>
         <v>520000</v>
       </c>
       <c r="F10" s="3">
@@ -1723,12 +1726,177 @@
       <c r="Q10" s="4"/>
       <c r="R10" s="4"/>
     </row>
+    <row r="11" spans="1:18">
+      <c r="A11" s="1">
+        <v>3004021</v>
+      </c>
+      <c r="B11" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D11" s="2">
+        <v>1</v>
+      </c>
+      <c r="E11" s="3">
+        <f t="shared" si="0"/>
+        <v>5200</v>
+      </c>
+      <c r="F11" s="3">
+        <v>100</v>
+      </c>
+      <c r="G11" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H11" s="3">
+        <v>1</v>
+      </c>
+      <c r="I11" s="3">
+        <v>4</v>
+      </c>
+      <c r="J11" s="3">
+        <v>2</v>
+      </c>
+      <c r="K11" s="3">
+        <v>6</v>
+      </c>
+      <c r="L11" s="4">
+        <v>8</v>
+      </c>
+      <c r="M11" s="4">
+        <v>10</v>
+      </c>
+      <c r="N11" s="3">
+        <v>6</v>
+      </c>
+      <c r="O11" s="4">
+        <v>8</v>
+      </c>
+      <c r="P11" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q11" s="4" t="s">
+        <v>34</v>
+      </c>
+      <c r="R11" s="4" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18">
+      <c r="A12" s="1">
+        <v>3004022</v>
+      </c>
+      <c r="B12" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D12" s="1">
+        <v>2</v>
+      </c>
+      <c r="E12" s="3">
+        <f t="shared" si="0"/>
+        <v>52000</v>
+      </c>
+      <c r="F12" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G12" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H12" s="3">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
+        <v>4</v>
+      </c>
+      <c r="J12" s="3">
+        <v>2</v>
+      </c>
+      <c r="K12" s="3">
+        <v>6</v>
+      </c>
+      <c r="L12" s="4">
+        <v>8</v>
+      </c>
+      <c r="M12" s="4">
+        <v>10</v>
+      </c>
+      <c r="N12" s="3">
+        <v>6</v>
+      </c>
+      <c r="O12" s="4">
+        <v>8</v>
+      </c>
+      <c r="P12" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q12" s="4"/>
+      <c r="R12" s="4"/>
+    </row>
+    <row r="13" spans="1:18">
+      <c r="A13" s="1">
+        <v>3004023</v>
+      </c>
+      <c r="B13" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="D13" s="1">
+        <v>3</v>
+      </c>
+      <c r="E13" s="3">
+        <f t="shared" si="0"/>
+        <v>520000</v>
+      </c>
+      <c r="F13" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G13" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H13" s="3">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
+        <v>4</v>
+      </c>
+      <c r="J13" s="3">
+        <v>2</v>
+      </c>
+      <c r="K13" s="3">
+        <v>6</v>
+      </c>
+      <c r="L13" s="4">
+        <v>8</v>
+      </c>
+      <c r="M13" s="4">
+        <v>10</v>
+      </c>
+      <c r="N13" s="3">
+        <v>6</v>
+      </c>
+      <c r="O13" s="4">
+        <v>8</v>
+      </c>
+      <c r="P13" s="4">
+        <v>10</v>
+      </c>
+      <c r="Q13" s="4"/>
+      <c r="R13" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="6">
     <mergeCell ref="Q5:Q7"/>
     <mergeCell ref="Q8:Q10"/>
+    <mergeCell ref="Q11:Q13"/>
     <mergeCell ref="R5:R7"/>
     <mergeCell ref="R8:R10"/>
+    <mergeCell ref="R11:R13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -1728,7 +1728,7 @@
     </row>
     <row r="11" spans="1:18">
       <c r="A11" s="1">
-        <v>3004021</v>
+        <v>30040231</v>
       </c>
       <c r="B11" s="2">
         <v>300402</v>
@@ -1785,7 +1785,7 @@
     </row>
     <row r="12" spans="1:18">
       <c r="A12" s="1">
-        <v>3004022</v>
+        <v>30040232</v>
       </c>
       <c r="B12" s="2">
         <v>300402</v>
@@ -1838,7 +1838,7 @@
     </row>
     <row r="13" spans="1:18">
       <c r="A13" s="1">
-        <v>3004023</v>
+        <v>30040233</v>
       </c>
       <c r="B13" s="2">
         <v>300402</v>

--- a/poker/resources/sample/SouthernMoney.xlsx
+++ b/poker/resources/sample/SouthernMoney.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView windowWidth="27945" windowHeight="11925"/>
   </bookViews>
   <sheets>
     <sheet name="SouthernMoney" sheetId="1" r:id="rId1"/>
@@ -157,7 +157,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="80" uniqueCount="43">
   <si>
     <t>id</t>
   </si>
@@ -285,6 +285,9 @@
   </si>
   <si>
     <t>最终赢分=名次赢奖+剩余手牌2赢奖+剩余炸弹赢奖（炸弹结算是在牌局中即时结算）</t>
+  </si>
+  <si>
+    <t>南方前进-体验场</t>
   </si>
 </sst>
 </file>
@@ -1249,7 +1252,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:S19"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="12.5" style="1" customWidth="1"/>
@@ -1462,7 +1465,7 @@
         <v>1</v>
       </c>
       <c r="E5" s="3">
-        <f>F5*52</f>
+        <f t="shared" ref="E5:E10" si="0">F5*52</f>
         <v>5200</v>
       </c>
       <c r="F5" s="3">
@@ -1520,7 +1523,7 @@
         <v>2</v>
       </c>
       <c r="E6" s="3">
-        <f>F6*52</f>
+        <f t="shared" si="0"/>
         <v>52000</v>
       </c>
       <c r="F6" s="3">
@@ -1574,7 +1577,7 @@
         <v>3</v>
       </c>
       <c r="E7" s="3">
-        <f>F7*52</f>
+        <f t="shared" si="0"/>
         <v>520000</v>
       </c>
       <c r="F7" s="3">
@@ -1628,7 +1631,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="3">
-        <f>F8*52</f>
+        <f t="shared" si="0"/>
         <v>5200</v>
       </c>
       <c r="F8" s="3">
@@ -1686,7 +1689,7 @@
         <v>2</v>
       </c>
       <c r="E9" s="3">
-        <f>F9*52</f>
+        <f t="shared" si="0"/>
         <v>52000</v>
       </c>
       <c r="F9" s="3">
@@ -1740,7 +1743,7 @@
         <v>3</v>
       </c>
       <c r="E10" s="3">
-        <f>F10*52</f>
+        <f t="shared" si="0"/>
         <v>520000</v>
       </c>
       <c r="F10" s="3">
@@ -1794,7 +1797,7 @@
         <v>1</v>
       </c>
       <c r="E11" s="3">
-        <f>F11*12</f>
+        <f t="shared" ref="E11:E16" si="1">F11*12</f>
         <v>12000</v>
       </c>
       <c r="F11" s="3">
@@ -1849,7 +1852,7 @@
         <v>2</v>
       </c>
       <c r="E12" s="3">
-        <f>F12*12</f>
+        <f t="shared" si="1"/>
         <v>120000</v>
       </c>
       <c r="F12" s="3">
@@ -1902,7 +1905,7 @@
         <v>3</v>
       </c>
       <c r="E13" s="3">
-        <f>F13*12</f>
+        <f t="shared" si="1"/>
         <v>1200000</v>
       </c>
       <c r="F13" s="3">
@@ -1955,7 +1958,7 @@
         <v>1</v>
       </c>
       <c r="E14" s="3">
-        <f>F14*12</f>
+        <f t="shared" si="1"/>
         <v>12000</v>
       </c>
       <c r="F14" s="3">
@@ -2010,7 +2013,7 @@
         <v>2</v>
       </c>
       <c r="E15" s="3">
-        <f>F15*12</f>
+        <f t="shared" si="1"/>
         <v>120000</v>
       </c>
       <c r="F15" s="3">
@@ -2063,7 +2066,7 @@
         <v>3</v>
       </c>
       <c r="E16" s="3">
-        <f>F16*12</f>
+        <f t="shared" si="1"/>
         <v>1200000</v>
       </c>
       <c r="F16" s="3">
@@ -2102,14 +2105,182 @@
       </c>
       <c r="R16" s="4"/>
     </row>
+    <row r="17" customFormat="1" spans="1:19">
+      <c r="A17" s="1">
+        <v>30040231</v>
+      </c>
+      <c r="B17" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="2">
+        <v>1</v>
+      </c>
+      <c r="E17" s="3">
+        <f t="shared" ref="E17:E19" si="2">F17*52</f>
+        <v>5200</v>
+      </c>
+      <c r="F17" s="3">
+        <v>100</v>
+      </c>
+      <c r="G17" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H17" s="1"/>
+      <c r="I17" s="3">
+        <v>1</v>
+      </c>
+      <c r="J17" s="3">
+        <v>4</v>
+      </c>
+      <c r="K17" s="3">
+        <v>2</v>
+      </c>
+      <c r="L17" s="3">
+        <v>6</v>
+      </c>
+      <c r="M17" s="4">
+        <v>8</v>
+      </c>
+      <c r="N17" s="4">
+        <v>10</v>
+      </c>
+      <c r="O17" s="3">
+        <v>6</v>
+      </c>
+      <c r="P17" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q17" s="4">
+        <v>10</v>
+      </c>
+      <c r="R17" s="4" t="s">
+        <v>37</v>
+      </c>
+      <c r="S17" s="4" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="18" customFormat="1" spans="1:19">
+      <c r="A18" s="1">
+        <v>30040232</v>
+      </c>
+      <c r="B18" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="3">
+        <f t="shared" si="2"/>
+        <v>52000</v>
+      </c>
+      <c r="F18" s="3">
+        <v>1000</v>
+      </c>
+      <c r="G18" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H18" s="1"/>
+      <c r="I18" s="3">
+        <v>1</v>
+      </c>
+      <c r="J18" s="3">
+        <v>4</v>
+      </c>
+      <c r="K18" s="3">
+        <v>2</v>
+      </c>
+      <c r="L18" s="3">
+        <v>6</v>
+      </c>
+      <c r="M18" s="4">
+        <v>8</v>
+      </c>
+      <c r="N18" s="4">
+        <v>10</v>
+      </c>
+      <c r="O18" s="3">
+        <v>6</v>
+      </c>
+      <c r="P18" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q18" s="4">
+        <v>10</v>
+      </c>
+      <c r="R18" s="4"/>
+      <c r="S18" s="4"/>
+    </row>
+    <row r="19" customFormat="1" spans="1:19">
+      <c r="A19" s="1">
+        <v>30040233</v>
+      </c>
+      <c r="B19" s="2">
+        <v>300402</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="D19" s="1">
+        <v>3</v>
+      </c>
+      <c r="E19" s="3">
+        <f t="shared" si="2"/>
+        <v>520000</v>
+      </c>
+      <c r="F19" s="3">
+        <v>10000</v>
+      </c>
+      <c r="G19" s="1">
+        <v>100003</v>
+      </c>
+      <c r="H19" s="1"/>
+      <c r="I19" s="3">
+        <v>1</v>
+      </c>
+      <c r="J19" s="3">
+        <v>4</v>
+      </c>
+      <c r="K19" s="3">
+        <v>2</v>
+      </c>
+      <c r="L19" s="3">
+        <v>6</v>
+      </c>
+      <c r="M19" s="4">
+        <v>8</v>
+      </c>
+      <c r="N19" s="4">
+        <v>10</v>
+      </c>
+      <c r="O19" s="3">
+        <v>6</v>
+      </c>
+      <c r="P19" s="4">
+        <v>8</v>
+      </c>
+      <c r="Q19" s="4">
+        <v>10</v>
+      </c>
+      <c r="R19" s="4"/>
+      <c r="S19" s="4"/>
+    </row>
   </sheetData>
-  <mergeCells count="6">
+  <mergeCells count="8">
     <mergeCell ref="R5:R7"/>
     <mergeCell ref="R8:R10"/>
     <mergeCell ref="R11:R13"/>
     <mergeCell ref="R14:R16"/>
+    <mergeCell ref="R17:R19"/>
     <mergeCell ref="S5:S7"/>
     <mergeCell ref="S8:S10"/>
+    <mergeCell ref="S17:S19"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
